--- a/business_forms/022_office_visit_scheduling_form--business_forms.xlsx
+++ b/business_forms/022_office_visit_scheduling_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['morning',_'afternoon',_'evening']</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['Morning', 'Afternoon', 'Evening']</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['09:00_-_10:00',_'10:00_-_11:00',_'11:00_-_12:00']</t>
+          <t>09:00_-_10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['09:00 - 10:00', '10:00 - 11:00', '11:00 - 12:00']</t>
+          <t>09:00 - 10:00</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['english',_'spanish',_'french']</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['English', 'Spanish', 'French']</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['individual',_'group']</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['Individual', 'Group']</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
